--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-participant-apsr.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-participant-apsr.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$55</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="242">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -694,6 +694,12 @@
   </si>
   <si>
     <t>ParticipantRole.code</t>
+  </si>
+  <si>
+    <t>Participant2.participantRole.sdtcSpecialty</t>
+  </si>
+  <si>
+    <t>ParticipantRole.sdtcSpecialty</t>
   </si>
   <si>
     <t>Participant2.participantRole.addr</t>
@@ -1081,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK54"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.8359375" customWidth="true" bestFit="true"/>
@@ -6119,7 +6125,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>219</v>
       </c>
@@ -6138,7 +6144,7 @@
         <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>74</v>
@@ -6147,11 +6153,9 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6202,7 +6206,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6222,10 +6226,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6248,10 +6252,10 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
@@ -6303,7 +6307,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6323,10 +6327,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6337,7 +6341,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>151</v>
@@ -6349,14 +6353,12 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -6406,13 +6408,13 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>74</v>
@@ -6426,10 +6428,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6452,13 +6454,13 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6509,7 +6511,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6527,12 +6529,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6546,7 +6548,7 @@
         <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>74</v>
@@ -6555,10 +6557,14 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6608,26 +6614,125 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK54" t="s" s="2">
+      <c r="B55" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK55" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK54">
+  <autoFilter ref="A1:AK55">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6637,7 +6742,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI53">
+  <conditionalFormatting sqref="A2:AI54">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
